--- a/TestCase/PhonePe.xlsx
+++ b/TestCase/PhonePe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\SDET_Wipro\TestCase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D2022B-5CB9-4C66-9805-71716E7D2C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5CF2B6-566C-4350-8AC3-C9D0804CD181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0D298D77-291B-48BF-8369-7064F5FC16AD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -245,9 +245,6 @@
   </si>
   <si>
     <t>TC016</t>
-  </si>
-  <si>
-    <t>TC017</t>
   </si>
   <si>
     <t>1. Button clickable and proceeds next
@@ -664,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57F7DEDA-4226-4CC6-A507-D6C749D52082}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="3" customWidth="1"/>
@@ -971,7 +968,7 @@
         <v>56</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -1037,7 +1034,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>24</v>
@@ -1060,7 +1057,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>24</v>
@@ -1074,27 +1071,19 @@
         <v>64</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
